--- a/20_設計書/化学物質データ画面.xlsx
+++ b/20_設計書/化学物質データ画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB98085-784B-4D6E-A24B-AB5BEF5687F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EA7E5E-F3F7-4979-AE12-80F536B84BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32220" yWindow="3420" windowWidth="16245" windowHeight="10095" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="244">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -1578,40 +1578,6 @@
     <phoneticPr fontId="53"/>
   </si>
   <si>
-    <t>証明書申請テーブルから以下条件でデータを取得して画面「検索結果表示」エリアに表示する</t>
-    <rPh sb="0" eb="3">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジョウケン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="53"/>
-  </si>
-  <si>
     <t>ユーザコード</t>
     <phoneticPr fontId="55"/>
   </si>
@@ -1659,57 +1625,7 @@
     <phoneticPr fontId="11"/>
   </si>
   <si>
-    <t>証明書申請テーブル、証明書申請入力</t>
-    <rPh sb="0" eb="3">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
     <t>テーブル</t>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
-    <t>証明書申請テーブル 受付番号=検索結果対象明細.申請番号</t>
-    <rPh sb="0" eb="3">
-      <t>ショウメイショ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>ウケツケバンゴウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>メイサイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>バンゴウ</t>
-    </rPh>
     <phoneticPr fontId="55"/>
   </si>
   <si>
@@ -2079,22 +1995,6 @@
       <t>デンキ</t>
     </rPh>
     <rPh sb="52" eb="54">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="53"/>
-  </si>
-  <si>
-    <t>リンクを押下すると「化学物質データ」画面に遷移する</t>
-    <rPh sb="4" eb="6">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="53"/>
@@ -2351,6 +2251,100 @@
       <t>シンカンキョウショウメイショ</t>
     </rPh>
     <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>申請テーブルから以下条件でデータを取得して画面「検索結果表示」エリアに表示する</t>
+    <rPh sb="8" eb="10">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="53"/>
+  </si>
+  <si>
+    <t>申請テーブル、証明書申請入力</t>
+    <rPh sb="7" eb="10">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>申請テーブル 受付番号=検索結果対象明細.申請番号</t>
+    <rPh sb="7" eb="11">
+      <t>ウケツケバンゴウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>メイサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>申請者アカウントID</t>
+    <rPh sb="0" eb="3">
+      <t>シンセイシャ</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>ホーム画面: ホーム (リンクなし)</t>
+    <phoneticPr fontId="53"/>
+  </si>
+  <si>
+    <t>dr1.5</t>
+    <phoneticPr fontId="49"/>
+  </si>
+  <si>
+    <t>課題リストの回答をもとに修正</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="49"/>
   </si>
 </sst>
 </file>
@@ -10288,7 +10282,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
       <c r="B22" s="184" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 11日 dr1.4</v>
+        <v>2026年 06月 17日 dr1.5</v>
       </c>
       <c r="C22" s="185"/>
       <c r="D22" s="185"/>
@@ -11305,7 +11299,7 @@
     </row>
     <row r="2" spans="1:53">
       <c r="A2" s="212" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B2" s="212"/>
       <c r="C2" s="212"/>
@@ -11321,7 +11315,7 @@
       <c r="K2" s="213"/>
       <c r="L2" s="213"/>
       <c r="M2" s="214" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N2" s="215"/>
       <c r="O2" s="215"/>
@@ -11362,7 +11356,7 @@
       <c r="AR2" s="217"/>
       <c r="AS2" s="217"/>
       <c r="AT2" s="220">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AU2" s="220"/>
       <c r="AV2" s="220"/>
@@ -11432,7 +11426,7 @@
       <c r="AS3" s="217"/>
       <c r="AT3" s="233" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>dr1.4</v>
+        <v>dr1.5</v>
       </c>
       <c r="AU3" s="233"/>
       <c r="AV3" s="233"/>
@@ -11522,7 +11516,7 @@
       <c r="O6" s="219"/>
       <c r="P6" s="219"/>
       <c r="Q6" s="219" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="R6" s="219"/>
       <c r="S6" s="219"/>
@@ -11571,7 +11565,7 @@
     </row>
     <row r="7" spans="1:53">
       <c r="A7" s="191" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B7" s="191"/>
       <c r="C7" s="192" t="s">
@@ -11634,11 +11628,11 @@
     </row>
     <row r="8" spans="1:53" ht="44.5" customHeight="1">
       <c r="A8" s="206" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B8" s="207"/>
       <c r="C8" s="193" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D8" s="193"/>
       <c r="E8" s="193"/>
@@ -11654,7 +11648,7 @@
       <c r="O8" s="193"/>
       <c r="P8" s="193"/>
       <c r="Q8" s="203" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="R8" s="204"/>
       <c r="S8" s="204"/>
@@ -11699,11 +11693,11 @@
     </row>
     <row r="9" spans="1:53" ht="23.5" customHeight="1">
       <c r="A9" s="206" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B9" s="207"/>
       <c r="C9" s="193" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D9" s="193"/>
       <c r="E9" s="193"/>
@@ -11764,11 +11758,11 @@
     </row>
     <row r="10" spans="1:53" ht="51" customHeight="1">
       <c r="A10" s="206" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B10" s="207"/>
       <c r="C10" s="193" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D10" s="193"/>
       <c r="E10" s="193"/>
@@ -11784,7 +11778,7 @@
       <c r="O10" s="193"/>
       <c r="P10" s="193"/>
       <c r="Q10" s="193" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="R10" s="192"/>
       <c r="S10" s="192"/>
@@ -11829,11 +11823,11 @@
     </row>
     <row r="11" spans="1:53" ht="37.5" customHeight="1">
       <c r="A11" s="206" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B11" s="207"/>
       <c r="C11" s="193" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D11" s="193"/>
       <c r="E11" s="193"/>
@@ -11849,7 +11843,7 @@
       <c r="O11" s="193"/>
       <c r="P11" s="193"/>
       <c r="Q11" s="193" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R11" s="192"/>
       <c r="S11" s="192"/>
@@ -11892,10 +11886,14 @@
       <c r="AZ11" s="192"/>
       <c r="BA11" s="192"/>
     </row>
-    <row r="12" spans="1:53">
-      <c r="A12" s="191"/>
-      <c r="B12" s="191"/>
-      <c r="C12" s="193"/>
+    <row r="12" spans="1:53" ht="24.5" customHeight="1">
+      <c r="A12" s="206" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="207"/>
+      <c r="C12" s="193" t="s">
+        <v>203</v>
+      </c>
       <c r="D12" s="193"/>
       <c r="E12" s="193"/>
       <c r="F12" s="193"/>
@@ -11909,7 +11907,9 @@
       <c r="N12" s="193"/>
       <c r="O12" s="193"/>
       <c r="P12" s="193"/>
-      <c r="Q12" s="192"/>
+      <c r="Q12" s="192" t="s">
+        <v>243</v>
+      </c>
       <c r="R12" s="192"/>
       <c r="S12" s="192"/>
       <c r="T12" s="192"/>
@@ -11930,11 +11930,15 @@
       <c r="AI12" s="192"/>
       <c r="AJ12" s="192"/>
       <c r="AK12" s="192"/>
-      <c r="AL12" s="190"/>
+      <c r="AL12" s="190">
+        <v>46190</v>
+      </c>
       <c r="AM12" s="191"/>
       <c r="AN12" s="191"/>
       <c r="AO12" s="191"/>
-      <c r="AP12" s="192"/>
+      <c r="AP12" s="192" t="s">
+        <v>29</v>
+      </c>
       <c r="AQ12" s="192"/>
       <c r="AR12" s="192"/>
       <c r="AS12" s="192"/>
@@ -13559,7 +13563,7 @@
       <c r="AU2" s="217"/>
       <c r="AV2" s="220">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AW2" s="233"/>
       <c r="AX2" s="233"/>
@@ -13611,7 +13615,7 @@
       <c r="Z3" s="213"/>
       <c r="AA3" s="229" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
-        <v>変更来歴画面</v>
+        <v>表紙画面</v>
       </c>
       <c r="AB3" s="229"/>
       <c r="AC3" s="229"/>
@@ -13637,7 +13641,7 @@
       <c r="AU3" s="217"/>
       <c r="AV3" s="233" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>dr1.4</v>
+        <v>dr1.5</v>
       </c>
       <c r="AW3" s="233"/>
       <c r="AX3" s="233"/>
@@ -13651,7 +13655,7 @@
     <row r="5" spans="1:85" ht="13.5" customHeight="1">
       <c r="A5" s="259" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
-        <v>画面レイアウト(変更来歴)</v>
+        <v>画面レイアウト(表紙)</v>
       </c>
       <c r="B5" s="260"/>
       <c r="C5" s="260"/>
@@ -14065,7 +14069,7 @@
       <c r="BC9" s="50"/>
       <c r="BD9" s="34"/>
       <c r="BE9" s="236" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BF9" s="236"/>
       <c r="BG9" s="236"/>
@@ -15067,7 +15071,7 @@
       <c r="BE22" s="175"/>
       <c r="BF22" s="124"/>
       <c r="BG22" s="124" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="BH22" s="124"/>
       <c r="BI22" s="124"/>
@@ -15140,7 +15144,7 @@
       <c r="BE23" s="175"/>
       <c r="BF23" s="124"/>
       <c r="BG23" s="124" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="BH23" s="124"/>
       <c r="BI23" s="124"/>
@@ -16487,55 +16491,55 @@
     <row r="41" spans="1:72" ht="21.5" customHeight="1">
       <c r="A41" s="35"/>
       <c r="B41" s="249" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C41" s="249"/>
       <c r="D41" s="249"/>
       <c r="E41" s="249"/>
       <c r="F41" s="249" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G41" s="249"/>
       <c r="H41" s="249"/>
       <c r="I41" s="249"/>
       <c r="J41" s="249" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K41" s="249"/>
       <c r="L41" s="249"/>
       <c r="M41" s="249"/>
       <c r="N41" s="249" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O41" s="249"/>
       <c r="P41" s="249"/>
       <c r="Q41" s="249"/>
       <c r="R41" s="249" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="S41" s="249"/>
       <c r="T41" s="249"/>
       <c r="U41" s="249"/>
       <c r="V41" s="249" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="W41" s="249"/>
       <c r="X41" s="249"/>
       <c r="Y41" s="249"/>
       <c r="Z41" s="249" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AA41" s="249"/>
       <c r="AB41" s="249"/>
       <c r="AC41" s="249"/>
       <c r="AD41" s="249" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AE41" s="249"/>
       <c r="AF41" s="249"/>
       <c r="AG41" s="249"/>
       <c r="AH41" s="239" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AI41" s="240"/>
       <c r="AJ41" s="240"/>
@@ -16553,7 +16557,7 @@
       <c r="AR41" s="240"/>
       <c r="AS41" s="241"/>
       <c r="AT41" s="239" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AU41" s="240"/>
       <c r="AV41" s="240"/>
@@ -27781,7 +27785,7 @@
       <c r="AG3" s="320"/>
       <c r="AH3" s="320"/>
       <c r="AI3" s="314" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AJ3" s="320"/>
       <c r="AK3" s="320"/>
@@ -27915,11 +27919,11 @@
     </row>
     <row r="5" spans="1:78">
       <c r="A5" s="281" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B5" s="282"/>
       <c r="C5" s="287" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D5" s="288"/>
       <c r="E5" s="288"/>
@@ -27999,7 +28003,7 @@
     </row>
     <row r="6" spans="1:78" ht="29.5" customHeight="1">
       <c r="A6" s="281" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B6" s="282"/>
       <c r="C6" s="287"/>
@@ -28010,7 +28014,7 @@
       <c r="H6" s="288"/>
       <c r="I6" s="289"/>
       <c r="J6" s="290" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K6" s="291"/>
       <c r="L6" s="291"/>
@@ -28046,7 +28050,7 @@
       <c r="AP6" s="279"/>
       <c r="AQ6" s="279"/>
       <c r="AR6" s="278" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AS6" s="279"/>
       <c r="AT6" s="279"/>
@@ -28216,7 +28220,7 @@
       <c r="AP8" s="279"/>
       <c r="AQ8" s="279"/>
       <c r="AR8" s="278" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AS8" s="279"/>
       <c r="AT8" s="279"/>
@@ -28386,7 +28390,7 @@
       <c r="AP10" s="295"/>
       <c r="AQ10" s="295"/>
       <c r="AR10" s="278" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AS10" s="279"/>
       <c r="AT10" s="279"/>
@@ -28436,7 +28440,7 @@
       <c r="H11" s="142"/>
       <c r="I11" s="143"/>
       <c r="J11" s="283" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K11" s="284"/>
       <c r="L11" s="284"/>
@@ -28463,7 +28467,7 @@
       <c r="AG11" s="295"/>
       <c r="AH11" s="295"/>
       <c r="AI11" s="294" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="AJ11" s="295"/>
       <c r="AK11" s="295"/>
@@ -28511,7 +28515,7 @@
     </row>
     <row r="12" spans="1:78" ht="39" customHeight="1">
       <c r="A12" s="281" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B12" s="282"/>
       <c r="C12" s="141"/>
@@ -28522,7 +28526,7 @@
       <c r="H12" s="142"/>
       <c r="I12" s="143"/>
       <c r="J12" s="283" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K12" s="284"/>
       <c r="L12" s="284"/>
@@ -28549,7 +28553,7 @@
       <c r="AG12" s="295"/>
       <c r="AH12" s="295"/>
       <c r="AI12" s="294" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="AJ12" s="295"/>
       <c r="AK12" s="295"/>
@@ -28560,7 +28564,7 @@
       <c r="AP12" s="295"/>
       <c r="AQ12" s="295"/>
       <c r="AR12" s="278" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AS12" s="279"/>
       <c r="AT12" s="279"/>
@@ -28599,7 +28603,7 @@
     </row>
     <row r="13" spans="1:78" ht="20" customHeight="1">
       <c r="A13" s="281" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B13" s="282"/>
       <c r="C13" s="141"/>
@@ -28646,7 +28650,7 @@
       <c r="AP13" s="295"/>
       <c r="AQ13" s="295"/>
       <c r="AR13" s="278" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AS13" s="279"/>
       <c r="AT13" s="279"/>
@@ -28732,7 +28736,7 @@
       <c r="AP14" s="279"/>
       <c r="AQ14" s="279"/>
       <c r="AR14" s="278" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AS14" s="279"/>
       <c r="AT14" s="279"/>
@@ -28981,7 +28985,7 @@
       <c r="AG17" s="279"/>
       <c r="AH17" s="279"/>
       <c r="AI17" s="286" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AJ17" s="279"/>
       <c r="AK17" s="279"/>
@@ -28992,7 +28996,7 @@
       <c r="AP17" s="279"/>
       <c r="AQ17" s="279"/>
       <c r="AR17" s="302" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AS17" s="303"/>
       <c r="AT17" s="303"/>
@@ -29069,7 +29073,7 @@
       <c r="AG18" s="297"/>
       <c r="AH18" s="297"/>
       <c r="AI18" s="286" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AJ18" s="279"/>
       <c r="AK18" s="279"/>
@@ -29155,7 +29159,7 @@
       <c r="AG19" s="145"/>
       <c r="AH19" s="145"/>
       <c r="AI19" s="286" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AJ19" s="279"/>
       <c r="AK19" s="279"/>
@@ -29241,7 +29245,7 @@
       <c r="AG20" s="145"/>
       <c r="AH20" s="145"/>
       <c r="AI20" s="286" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AJ20" s="279"/>
       <c r="AK20" s="279"/>
@@ -29329,7 +29333,7 @@
       <c r="AG21" s="297"/>
       <c r="AH21" s="298"/>
       <c r="AI21" s="286" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AJ21" s="279"/>
       <c r="AK21" s="279"/>
@@ -29496,7 +29500,7 @@
       <c r="Z23" s="145"/>
       <c r="AA23" s="146"/>
       <c r="AB23" s="296" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AC23" s="297"/>
       <c r="AD23" s="297"/>
@@ -29505,7 +29509,7 @@
       <c r="AG23" s="297"/>
       <c r="AH23" s="298"/>
       <c r="AI23" s="286" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AJ23" s="279"/>
       <c r="AK23" s="279"/>
@@ -29586,7 +29590,7 @@
       <c r="Z24" s="279"/>
       <c r="AA24" s="293"/>
       <c r="AB24" s="286" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AC24" s="279"/>
       <c r="AD24" s="279"/>
@@ -29595,7 +29599,7 @@
       <c r="AG24" s="279"/>
       <c r="AH24" s="279"/>
       <c r="AI24" s="286" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AJ24" s="279"/>
       <c r="AK24" s="279"/>
@@ -29606,7 +29610,7 @@
       <c r="AP24" s="279"/>
       <c r="AQ24" s="279"/>
       <c r="AR24" s="278" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AS24" s="279"/>
       <c r="AT24" s="279"/>
@@ -29864,7 +29868,7 @@
       <c r="AP27" s="279"/>
       <c r="AQ27" s="279"/>
       <c r="AR27" s="299" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AS27" s="300"/>
       <c r="AT27" s="300"/>
@@ -30291,14 +30295,14 @@
     <row r="5" spans="1:85">
       <c r="A5" s="160"/>
       <c r="C5" s="156" t="s">
-        <v>173</v>
+        <v>237</v>
       </c>
       <c r="CG5" s="161"/>
     </row>
     <row r="6" spans="1:85" ht="15" customHeight="1">
       <c r="A6" s="160"/>
       <c r="C6" s="328" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="329"/>
       <c r="E6" s="329"/>
@@ -30309,7 +30313,7 @@
       <c r="J6" s="329"/>
       <c r="K6" s="330"/>
       <c r="L6" s="328" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M6" s="329"/>
       <c r="N6" s="329"/>
@@ -30333,7 +30337,7 @@
     <row r="7" spans="1:85" ht="15" customHeight="1">
       <c r="A7" s="160"/>
       <c r="C7" s="334" t="s">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="D7" s="335"/>
       <c r="E7" s="335"/>
@@ -30344,7 +30348,7 @@
       <c r="J7" s="335"/>
       <c r="K7" s="336"/>
       <c r="L7" s="331" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M7" s="332"/>
       <c r="N7" s="332"/>
@@ -30373,14 +30377,14 @@
     <row r="9" spans="1:85">
       <c r="A9" s="160"/>
       <c r="B9" s="156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CG9" s="161"/>
     </row>
     <row r="10" spans="1:85" hidden="1">
       <c r="A10" s="160"/>
       <c r="C10" s="328" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D10" s="329"/>
       <c r="E10" s="329"/>
@@ -30391,7 +30395,7 @@
       <c r="J10" s="329"/>
       <c r="K10" s="330"/>
       <c r="L10" s="328" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M10" s="329"/>
       <c r="N10" s="329"/>
@@ -30415,7 +30419,7 @@
     <row r="11" spans="1:85" hidden="1">
       <c r="A11" s="160"/>
       <c r="C11" s="334" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D11" s="335"/>
       <c r="E11" s="335"/>
@@ -30426,7 +30430,7 @@
       <c r="J11" s="335"/>
       <c r="K11" s="336"/>
       <c r="L11" s="331" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M11" s="332"/>
       <c r="N11" s="332"/>
@@ -30455,14 +30459,14 @@
     <row r="13" spans="1:85">
       <c r="A13" s="160"/>
       <c r="D13" s="182" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="CG13" s="161"/>
     </row>
     <row r="14" spans="1:85" ht="15" customHeight="1">
       <c r="A14" s="160"/>
       <c r="D14" s="324" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E14" s="324"/>
       <c r="F14" s="324"/>
@@ -30481,7 +30485,7 @@
       <c r="S14" s="324"/>
       <c r="T14" s="324"/>
       <c r="U14" s="325" t="s">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="V14" s="326"/>
       <c r="W14" s="326"/>
@@ -30539,7 +30543,7 @@
       <c r="S15" s="324"/>
       <c r="T15" s="324"/>
       <c r="U15" s="325" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="V15" s="326"/>
       <c r="W15" s="326"/>
@@ -30578,7 +30582,7 @@
     <row r="16" spans="1:85">
       <c r="A16" s="160"/>
       <c r="D16" s="181" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="CG16" s="161"/>
     </row>
@@ -30596,7 +30600,7 @@
     <row r="19" spans="1:85">
       <c r="A19" s="160"/>
       <c r="B19" s="156" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C19" s="182"/>
       <c r="CG19" s="161"/>
